--- a/artfynd/S 6544-2021 artfynd.xlsx
+++ b/artfynd/S 6544-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY145"/>
+  <dimension ref="A1:AZ145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304882</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304907</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305126</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305127</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305128</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305129</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305130</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304950</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304951</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304952</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304953</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304958</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304959</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304960</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304962</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304963</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305256</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305257</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305258</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305259</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305261</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305263</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305264</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305265</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305266</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3298,6 +3428,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305267</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305268</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3496,6 +3636,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389463</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3593,6 +3738,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389467</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3690,6 +3840,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389470</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3787,6 +3942,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389485</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3884,6 +4044,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389489</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3981,6 +4146,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389493</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4078,6 +4248,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389505</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4175,6 +4350,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389506</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4272,6 +4452,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389513</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4369,6 +4554,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389515</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4470,6 +4660,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304917</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4571,6 +4766,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305178</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4672,6 +4872,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305179</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4773,6 +4978,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305180</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4874,6 +5084,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305181</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4975,6 +5190,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305182</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5076,6 +5296,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305183</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5177,6 +5402,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305184</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5278,6 +5508,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305186</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5379,6 +5614,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305187</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5480,6 +5720,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305188</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5577,6 +5822,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389468</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5674,6 +5924,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389472</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5771,6 +6026,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389496</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5868,6 +6128,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389498</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5965,6 +6230,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389503</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6062,6 +6332,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389511</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6163,6 +6438,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304943</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6264,6 +6544,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304944</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6365,6 +6650,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305247</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6466,6 +6756,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305248</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6567,6 +6862,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305249</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6668,6 +6968,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305250</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6765,6 +7070,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389501</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6866,6 +7176,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305073</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6967,6 +7282,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305074</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7073,6 +7393,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304857</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7174,6 +7499,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305221</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7275,6 +7605,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305030</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7376,6 +7711,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305031</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7477,6 +7817,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305032</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7578,6 +7923,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305033</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7679,6 +8029,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305034</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7780,6 +8135,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305035</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7881,6 +8241,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305057</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7982,6 +8347,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305058</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8083,6 +8453,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305059</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8184,6 +8559,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305060</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8285,6 +8665,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305061</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8386,6 +8771,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305062</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8487,6 +8877,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305063</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8588,6 +8983,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305064</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8689,6 +9089,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305065</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8790,6 +9195,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305066</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8891,6 +9301,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305067</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8992,6 +9407,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305068</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9093,6 +9513,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305438</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9194,6 +9619,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305441</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9295,6 +9725,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305442</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9396,6 +9831,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305443</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9497,6 +9937,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305444</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9598,6 +10043,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305445</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9699,6 +10149,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305446</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9800,6 +10255,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305447</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9901,6 +10361,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305448</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10002,6 +10467,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305449</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10099,6 +10569,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389465</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10196,6 +10671,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389473</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10293,6 +10773,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389482</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10390,6 +10875,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389486</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10487,6 +10977,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389495</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10588,6 +11083,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305411</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10689,6 +11189,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304981</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10790,6 +11295,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304988</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10891,6 +11401,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304929</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10992,6 +11507,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305231</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11094,6 +11614,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120353866</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11195,6 +11720,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305216</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11296,6 +11826,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304990</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11397,6 +11932,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304991</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11498,6 +12038,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305098</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11599,6 +12144,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304860</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11700,6 +12250,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305024</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11801,6 +12356,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305025</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11902,6 +12462,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305076</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12003,6 +12568,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305347</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12104,6 +12674,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305348</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12205,6 +12780,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305361</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12302,6 +12882,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389464</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12399,6 +12984,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389492</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12496,6 +13086,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389497</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12597,6 +13192,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304858</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12698,6 +13298,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304966</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12799,6 +13404,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305275</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12900,6 +13510,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305276</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13001,6 +13616,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305279</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13102,6 +13722,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305280</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13203,6 +13828,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305286</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13304,6 +13934,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305287</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13405,6 +14040,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305079</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13506,6 +14146,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305080</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13607,6 +14252,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305081</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13708,6 +14358,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305083</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13809,6 +14464,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305084</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13910,6 +14570,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305085</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14011,6 +14676,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305091</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14112,6 +14782,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305092</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14213,6 +14888,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305093</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14314,6 +14994,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305471</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14415,6 +15100,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305472</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14516,6 +15206,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305473</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14617,6 +15312,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305486</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14718,6 +15418,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305487</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14819,6 +15524,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305488</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14916,6 +15626,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389466</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15013,6 +15728,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129389502</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15127,8 +15847,159 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134124849</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>